--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270552</v>
       </c>
       <c r="B2" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270540</v>
       </c>
       <c r="B3" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270543</v>
       </c>
       <c r="B4" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137270542</v>
       </c>
       <c r="B5" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>137270566</v>
       </c>
       <c r="B6" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270572</v>
       </c>
       <c r="B7" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92341</v>
+        <v>92351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270549</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270570</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270546</v>
       </c>
       <c r="B11" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270563</v>
       </c>
       <c r="B12" t="n">
-        <v>78508</v>
+        <v>78518</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270551</v>
       </c>
       <c r="B15" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270554</v>
       </c>
       <c r="B16" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137270564</v>
       </c>
       <c r="B17" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137270536</v>
       </c>
       <c r="B18" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137270553</v>
       </c>
       <c r="B19" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>137270541</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>137270559</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>137270556</v>
       </c>
       <c r="B22" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>137270561</v>
       </c>
       <c r="B23" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137270544</v>
       </c>
       <c r="B24" t="n">
-        <v>83492</v>
+        <v>83502</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137270555</v>
       </c>
       <c r="B25" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,6 +3171,10 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogarna runt Dansjö, Ly lm</t>
@@ -3252,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3363,7 @@
         <v>137270567</v>
       </c>
       <c r="B27" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3470,7 @@
         <v>137270545</v>
       </c>
       <c r="B28" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3577,7 @@
         <v>137270562</v>
       </c>
       <c r="B29" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3684,7 @@
         <v>137270547</v>
       </c>
       <c r="B30" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3791,7 @@
         <v>137270569</v>
       </c>
       <c r="B31" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3898,7 @@
         <v>137270573</v>
       </c>
       <c r="B32" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4005,7 @@
         <v>137270539</v>
       </c>
       <c r="B33" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4112,7 @@
         <v>137270558</v>
       </c>
       <c r="B34" t="n">
-        <v>78508</v>
+        <v>78518</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270552</v>
       </c>
       <c r="B2" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270540</v>
       </c>
       <c r="B3" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270543</v>
       </c>
       <c r="B4" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137270542</v>
       </c>
       <c r="B5" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>137270566</v>
       </c>
       <c r="B6" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270572</v>
       </c>
       <c r="B7" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92352</v>
+        <v>92355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270549</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270570</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270546</v>
       </c>
       <c r="B11" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270563</v>
       </c>
       <c r="B12" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270551</v>
       </c>
       <c r="B15" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270554</v>
       </c>
       <c r="B16" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137270564</v>
       </c>
       <c r="B17" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137270536</v>
       </c>
       <c r="B18" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137270553</v>
       </c>
       <c r="B19" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>137270541</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>137270559</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>137270556</v>
       </c>
       <c r="B22" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>137270561</v>
       </c>
       <c r="B23" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137270544</v>
       </c>
       <c r="B24" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137270555</v>
       </c>
       <c r="B25" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137270567</v>
       </c>
       <c r="B27" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>137270545</v>
       </c>
       <c r="B28" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137270562</v>
       </c>
       <c r="B29" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>137270547</v>
       </c>
       <c r="B30" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>137270569</v>
       </c>
       <c r="B31" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>137270573</v>
       </c>
       <c r="B32" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>137270539</v>
       </c>
       <c r="B33" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>137270558</v>
       </c>
       <c r="B34" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92355</v>
+        <v>92357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270552</v>
       </c>
       <c r="B2" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270540</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270543</v>
       </c>
       <c r="B4" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137270542</v>
       </c>
       <c r="B5" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>137270566</v>
       </c>
       <c r="B6" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270572</v>
       </c>
       <c r="B7" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92357</v>
+        <v>92362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270549</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270570</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270546</v>
       </c>
       <c r="B11" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270563</v>
       </c>
       <c r="B12" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270551</v>
       </c>
       <c r="B15" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270554</v>
       </c>
       <c r="B16" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137270564</v>
       </c>
       <c r="B17" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137270536</v>
       </c>
       <c r="B18" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137270553</v>
       </c>
       <c r="B19" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>137270541</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>137270559</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>137270556</v>
       </c>
       <c r="B22" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>137270561</v>
       </c>
       <c r="B23" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137270544</v>
       </c>
       <c r="B24" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137270555</v>
       </c>
       <c r="B25" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137270567</v>
       </c>
       <c r="B27" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>137270545</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137270562</v>
       </c>
       <c r="B29" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>137270547</v>
       </c>
       <c r="B30" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>137270569</v>
       </c>
       <c r="B31" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>137270573</v>
       </c>
       <c r="B32" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>137270539</v>
       </c>
       <c r="B33" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>137270558</v>
       </c>
       <c r="B34" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270552</v>
       </c>
       <c r="B2" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270540</v>
       </c>
       <c r="B3" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270543</v>
       </c>
       <c r="B4" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137270542</v>
       </c>
       <c r="B5" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>137270566</v>
       </c>
       <c r="B6" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270572</v>
       </c>
       <c r="B7" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92362</v>
+        <v>92374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270549</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270570</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270546</v>
       </c>
       <c r="B11" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270563</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270551</v>
       </c>
       <c r="B15" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270554</v>
       </c>
       <c r="B16" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137270564</v>
       </c>
       <c r="B17" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137270536</v>
       </c>
       <c r="B18" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137270553</v>
       </c>
       <c r="B19" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>137270541</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>137270559</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>137270556</v>
       </c>
       <c r="B22" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>137270561</v>
       </c>
       <c r="B23" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137270544</v>
       </c>
       <c r="B24" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137270567</v>
       </c>
       <c r="B27" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>137270545</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137270562</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>137270547</v>
       </c>
       <c r="B30" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>137270569</v>
       </c>
       <c r="B31" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>137270573</v>
       </c>
       <c r="B32" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>137270539</v>
       </c>
       <c r="B33" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>137270558</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270552</v>
       </c>
       <c r="B2" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270540</v>
       </c>
       <c r="B3" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270543</v>
       </c>
       <c r="B4" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137270542</v>
       </c>
       <c r="B5" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>137270566</v>
       </c>
       <c r="B6" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270572</v>
       </c>
       <c r="B7" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92374</v>
+        <v>92375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270549</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270570</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270546</v>
       </c>
       <c r="B11" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270563</v>
       </c>
       <c r="B12" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270551</v>
       </c>
       <c r="B15" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270554</v>
       </c>
       <c r="B16" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137270564</v>
       </c>
       <c r="B17" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137270536</v>
       </c>
       <c r="B18" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137270553</v>
       </c>
       <c r="B19" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>137270541</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>137270559</v>
       </c>
       <c r="B21" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>137270556</v>
       </c>
       <c r="B22" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>137270561</v>
       </c>
       <c r="B23" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137270544</v>
       </c>
       <c r="B24" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137270567</v>
       </c>
       <c r="B27" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>137270545</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137270562</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>137270547</v>
       </c>
       <c r="B30" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>137270569</v>
       </c>
       <c r="B31" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>137270573</v>
       </c>
       <c r="B32" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>137270539</v>
       </c>
       <c r="B33" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>137270558</v>
       </c>
       <c r="B34" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270552</v>
       </c>
       <c r="B2" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270540</v>
       </c>
       <c r="B3" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270543</v>
       </c>
       <c r="B4" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137270542</v>
       </c>
       <c r="B5" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>137270566</v>
       </c>
       <c r="B6" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270572</v>
       </c>
       <c r="B7" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92375</v>
+        <v>92378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270549</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270570</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270546</v>
       </c>
       <c r="B11" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270563</v>
       </c>
       <c r="B12" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270551</v>
       </c>
       <c r="B15" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270554</v>
       </c>
       <c r="B16" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137270564</v>
       </c>
       <c r="B17" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137270536</v>
       </c>
       <c r="B18" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137270553</v>
       </c>
       <c r="B19" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>137270541</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>137270559</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>137270556</v>
       </c>
       <c r="B22" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>137270561</v>
       </c>
       <c r="B23" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137270544</v>
       </c>
       <c r="B24" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137270567</v>
       </c>
       <c r="B27" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>137270545</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137270562</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>137270547</v>
       </c>
       <c r="B30" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>137270569</v>
       </c>
       <c r="B31" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>137270573</v>
       </c>
       <c r="B32" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>137270539</v>
       </c>
       <c r="B33" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>137270558</v>
       </c>
       <c r="B34" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22895-2026 artfynd.xlsx
+++ b/artfynd/A 22895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270552</v>
       </c>
       <c r="B2" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270540</v>
       </c>
       <c r="B3" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270543</v>
       </c>
       <c r="B4" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137270542</v>
       </c>
       <c r="B5" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>137270566</v>
       </c>
       <c r="B6" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270572</v>
       </c>
       <c r="B7" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270535</v>
       </c>
       <c r="B8" t="n">
-        <v>92378</v>
+        <v>92382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270549</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270570</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270546</v>
       </c>
       <c r="B11" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270563</v>
       </c>
       <c r="B12" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270537</v>
       </c>
       <c r="B13" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270568</v>
       </c>
       <c r="B14" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270551</v>
       </c>
       <c r="B15" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270554</v>
       </c>
       <c r="B16" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137270564</v>
       </c>
       <c r="B17" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137270536</v>
       </c>
       <c r="B18" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137270553</v>
       </c>
       <c r="B19" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>137270541</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>137270559</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>137270556</v>
       </c>
       <c r="B22" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>137270561</v>
       </c>
       <c r="B23" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137270544</v>
       </c>
       <c r="B24" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137270555</v>
       </c>
       <c r="B25" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137270571</v>
       </c>
       <c r="B26" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137270567</v>
       </c>
       <c r="B27" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>137270545</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137270562</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>137270547</v>
       </c>
       <c r="B30" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>137270569</v>
       </c>
       <c r="B31" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>137270573</v>
       </c>
       <c r="B32" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>137270539</v>
       </c>
       <c r="B33" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>137270558</v>
       </c>
       <c r="B34" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
